--- a/exports/HAVELLS_full_report.xlsx
+++ b/exports/HAVELLS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>3.36</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1318</v>
+        <v>1303.1</v>
       </c>
       <c r="I2" t="n">
         <v>1305.865</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.46</v>
+        <v>-3.56</v>
       </c>
       <c r="L2" t="n">
-        <v>2.98</v>
+        <v>4.23</v>
       </c>
       <c r="M2" t="n">
         <v>0.29</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,25 +626,25 @@
         <v>5.89</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44636.55208333334</v>
+        <v>44637.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1134.45</v>
+        <v>1172.5</v>
       </c>
       <c r="I3" t="n">
         <v>1149.980304938198</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K3" t="n">
-        <v>12.94</v>
+        <v>10.02</v>
       </c>
       <c r="L3" t="n">
         <v>2.27</v>
       </c>
       <c r="M3" t="n">
-        <v>2.01</v>
+        <v>2.17</v>
       </c>
       <c r="N3" t="n">
         <v>4.5</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44685.38541666666</v>
+        <v>44685.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>1266.2</v>
+        <v>1251</v>
       </c>
       <c r="I4" t="n">
         <v>1260.782333720112</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>7.99</v>
+        <v>6.7</v>
       </c>
       <c r="L4" t="n">
         <v>6.52</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44746.55208333334</v>
+        <v>44747.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1131</v>
+        <v>1160</v>
       </c>
       <c r="I5" t="n">
         <v>1137.564723889111</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>61</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>9.59</v>
+        <v>7.27</v>
       </c>
       <c r="L5" t="n">
         <v>2.89</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.24</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44768.38541666666</v>
+        <v>44768.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>1215.45</v>
+        <v>1207.6</v>
       </c>
       <c r="I6" t="n">
         <v>1214.568597197513</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>4.78</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
         <v>2.14</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>6.03</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44771.55208333334</v>
+        <v>44774.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1248.8</v>
+        <v>1284.35</v>
       </c>
       <c r="I7" t="n">
         <v>1275.612924661961</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.41</v>
+        <v>-6.36</v>
       </c>
       <c r="L7" t="n">
-        <v>3.75</v>
+        <v>6.65</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="N7" t="n">
-        <v>1.86</v>
+        <v>3.22</v>
       </c>
       <c r="O7" t="n">
         <v>-1.1</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.29</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44795.38541666666</v>
+        <v>44795.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>1316.05</v>
+        <v>1288.5</v>
       </c>
       <c r="I8" t="n">
         <v>1295.771724255779</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>2.47</v>
+        <v>0.32</v>
       </c>
       <c r="L8" t="n">
         <v>2.75</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>6.43</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44802.55208333334</v>
+        <v>44803.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1344</v>
+        <v>1375.5</v>
       </c>
       <c r="I9" t="n">
         <v>1355.315196794205</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.31</v>
+        <v>-6.75</v>
       </c>
       <c r="L9" t="n">
-        <v>4.58</v>
+        <v>7.69</v>
       </c>
       <c r="M9" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="N9" t="n">
-        <v>1.51</v>
+        <v>2.58</v>
       </c>
       <c r="O9" t="n">
         <v>-4.18</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>5.74</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1359</v>
+        <v>1319.4</v>
       </c>
       <c r="I10" t="n">
         <v>1322.739452054181</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2</v>
+        <v>-4.08</v>
       </c>
       <c r="L10" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="M10" t="n">
         <v>0.62</v>
       </c>
       <c r="N10" t="n">
-        <v>1.11</v>
+        <v>4.08</v>
       </c>
       <c r="O10" t="n">
         <v>2.58</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.4</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44889.55208333334</v>
+        <v>44890.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1245.8</v>
+        <v>1248.35</v>
       </c>
       <c r="I11" t="n">
         <v>1247.383274681192</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>69.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K11" t="n">
-        <v>5.58</v>
+        <v>5.39</v>
       </c>
       <c r="L11" t="n">
         <v>3.71</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>4.16</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44902.38541666666</v>
+        <v>44902.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>1209.55</v>
+        <v>1205</v>
       </c>
       <c r="I12" t="n">
         <v>1208.47575554946</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.11</v>
+        <v>-3.47</v>
       </c>
       <c r="L12" t="n">
-        <v>3.23</v>
+        <v>3.78</v>
       </c>
       <c r="M12" t="n">
         <v>0.29</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>3.98</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44929.55208333334</v>
+        <v>44930.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1128.9</v>
+        <v>1141.6</v>
       </c>
       <c r="I13" t="n">
         <v>1139.569921749842</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>6.32</v>
+        <v>5.26</v>
       </c>
       <c r="L13" t="n">
         <v>1.55</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.69</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44946.38541666666</v>
+        <v>44946.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>1154.45</v>
+        <v>1152</v>
       </c>
       <c r="I14" t="n">
         <v>1152.515279536823</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>1.13</v>
+        <v>0.91</v>
       </c>
       <c r="L14" t="n">
         <v>1.87</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>6.48</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44965.38541666666</v>
+        <v>44965.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>1205.45</v>
+        <v>1235</v>
       </c>
       <c r="I15" t="n">
         <v>1226.614432595891</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.64</v>
+        <v>-7.2</v>
       </c>
       <c r="L15" t="n">
-        <v>5.66</v>
+        <v>7.2</v>
       </c>
       <c r="M15" t="n">
         <v>0.72</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6.3</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1181</v>
+        <v>1161.9</v>
       </c>
       <c r="I16" t="n">
         <v>1175.484757468842</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.37</v>
+        <v>-5.92</v>
       </c>
       <c r="L16" t="n">
-        <v>5.34</v>
+        <v>6.64</v>
       </c>
       <c r="M16" t="n">
         <v>0.18</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>4.98</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44986.38541666666</v>
+        <v>44986.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>1214.2</v>
+        <v>1216</v>
       </c>
       <c r="I17" t="n">
         <v>1215.879285736712</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.5</v>
+        <v>-4.66</v>
       </c>
       <c r="L17" t="n">
-        <v>4.74</v>
+        <v>4.82</v>
       </c>
       <c r="M17" t="n">
         <v>0.51</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>4.44</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1202</v>
+        <v>1170</v>
       </c>
       <c r="I18" t="n">
         <v>1175.358797404621</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.15</v>
+        <v>-3.78</v>
       </c>
       <c r="L18" t="n">
-        <v>2.04</v>
+        <v>3.97</v>
       </c>
       <c r="M18" t="n">
         <v>0.4</v>
       </c>
       <c r="N18" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
         <v>1.42</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.34</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45021.38541666666</v>
+        <v>45021.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>1193.3</v>
+        <v>1199.25</v>
       </c>
       <c r="I19" t="n">
         <v>1194.561711177657</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.99</v>
+        <v>-2.5</v>
       </c>
       <c r="L19" t="n">
         <v>3.58</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.94</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45068.55208333334</v>
+        <v>45069.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1263</v>
+        <v>1250.4</v>
       </c>
       <c r="I20" t="n">
         <v>1251.056427420653</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K20" t="n">
-        <v>5.32</v>
+        <v>4.27</v>
       </c>
       <c r="L20" t="n">
         <v>3.42</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,25 +1868,25 @@
         <v>4.31</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1289.65</v>
+        <v>1297</v>
       </c>
       <c r="I21" t="n">
         <v>1295.300121228742</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.14</v>
+        <v>-3.73</v>
       </c>
       <c r="L21" t="n">
-        <v>3.36</v>
+        <v>3.97</v>
       </c>
       <c r="M21" t="n">
-        <v>0.12</v>
+        <v>0.38</v>
       </c>
       <c r="N21" t="n">
         <v>1.97</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>3.61</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1324.15</v>
+        <v>1290.65</v>
       </c>
       <c r="I22" t="n">
         <v>1313.282381193038</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K22" t="n">
-        <v>2.09</v>
+        <v>-0.49</v>
       </c>
       <c r="L22" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="M22" t="n">
         <v>0.36</v>
       </c>
       <c r="N22" t="n">
-        <v>1.45</v>
+        <v>3.01</v>
       </c>
       <c r="O22" t="n">
         <v>0.79</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>5.56</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45124.55208333334</v>
+        <v>45125.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1294.1</v>
+        <v>1351.8</v>
       </c>
       <c r="I23" t="n">
         <v>1329.926525682669</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.27</v>
+        <v>-4.74</v>
       </c>
       <c r="L23" t="n">
-        <v>3.42</v>
+        <v>6.3</v>
       </c>
       <c r="M23" t="n">
-        <v>0.62</v>
+        <v>2.54</v>
       </c>
       <c r="N23" t="n">
-        <v>1.64</v>
+        <v>3.32</v>
       </c>
       <c r="O23" t="n">
         <v>-3.01</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>5.93</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45149.55208333334</v>
+        <v>45152.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1299.05</v>
+        <v>1277.55</v>
       </c>
       <c r="I24" t="n">
         <v>1283.802417883209</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.9</v>
+        <v>-5.49</v>
       </c>
       <c r="L24" t="n">
-        <v>5.19</v>
+        <v>5.68</v>
       </c>
       <c r="M24" t="n">
         <v>0.92</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>4.68</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45160.38541666666</v>
+        <v>45160.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>1316</v>
+        <v>1320.85</v>
       </c>
       <c r="I25" t="n">
         <v>1317.99175875421</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.01</v>
+        <v>-3.39</v>
       </c>
       <c r="L25" t="n">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="M25" t="n">
         <v>0.36</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>3.51</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45197.38541666666</v>
+        <v>45197.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>1385.95</v>
+        <v>1380</v>
       </c>
       <c r="I26" t="n">
         <v>1380.396806085509</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>36.83333333333334</v>
+        <v>37</v>
       </c>
       <c r="K26" t="n">
-        <v>4.93</v>
+        <v>4.48</v>
       </c>
       <c r="L26" t="n">
         <v>1.19</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.43</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45250.55208333334</v>
+        <v>45251.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1277</v>
+        <v>1299.75</v>
       </c>
       <c r="I27" t="n">
         <v>1293.521720406765</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>53</v>
+        <v>53.83333333333334</v>
       </c>
       <c r="K27" t="n">
-        <v>7.46</v>
+        <v>5.82</v>
       </c>
       <c r="L27" t="n">
         <v>3.26</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>3.86</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45311.38541666666</v>
+        <v>45311.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>1386.8</v>
+        <v>1370</v>
       </c>
       <c r="I28" t="n">
         <v>1378.241399884158</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>60</v>
+        <v>60.16666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="L28" t="n">
         <v>1.85</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>5.23</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45335.38541666666</v>
+        <v>45335.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>1336</v>
+        <v>1362.95</v>
       </c>
       <c r="I29" t="n">
         <v>1355.478303761945</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>23.83333333333333</v>
+        <v>24</v>
       </c>
       <c r="K29" t="n">
-        <v>2.48</v>
+        <v>0.51</v>
       </c>
       <c r="L29" t="n">
         <v>1.24</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.28</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>1493.85</v>
+        <v>1470.05</v>
       </c>
       <c r="I30" t="n">
         <v>1474.35738173608</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K30" t="n">
-        <v>9.6</v>
+        <v>7.86</v>
       </c>
       <c r="L30" t="n">
         <v>2.04</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>6.98</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45383.55208333334</v>
+        <v>45384.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1515</v>
+        <v>1542.65</v>
       </c>
       <c r="I31" t="n">
         <v>1541.829664558586</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.06</v>
+        <v>-4.94</v>
       </c>
       <c r="L31" t="n">
-        <v>4.69</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
         <v>0.65</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.38</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1882.65</v>
+        <v>1780.35</v>
       </c>
       <c r="I32" t="n">
         <v>1807.84659376699</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K32" t="n">
-        <v>22.04</v>
+        <v>15.41</v>
       </c>
       <c r="L32" t="n">
         <v>5.75</v>
@@ -2265,7 +2648,7 @@
         <v>1.92</v>
       </c>
       <c r="N32" t="n">
-        <v>1.91</v>
+        <v>6.29</v>
       </c>
       <c r="O32" t="n">
         <v>1.99</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>9.75</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45463.55208333334</v>
+        <v>45464.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1818.15</v>
+        <v>1893.75</v>
       </c>
       <c r="I33" t="n">
         <v>1893.396250203784</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.12</v>
+        <v>-6.37</v>
       </c>
       <c r="L33" t="n">
-        <v>5.93</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M33" t="n">
         <v>1.45</v>
       </c>
       <c r="N33" t="n">
-        <v>2.92</v>
+        <v>3.68</v>
       </c>
       <c r="O33" t="n">
         <v>-6.29</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.47</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45470.55208333334</v>
+        <v>45471.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1850</v>
+        <v>1829.35</v>
       </c>
       <c r="I34" t="n">
         <v>1832.426642217168</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.31</v>
+        <v>-3.4</v>
       </c>
       <c r="L34" t="n">
         <v>4</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>6.82</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45481.55208333334</v>
+        <v>45482.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1886.85</v>
+        <v>1915.15</v>
       </c>
       <c r="I35" t="n">
         <v>1913.896461986354</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.14</v>
+        <v>-4.69</v>
       </c>
       <c r="L35" t="n">
-        <v>4.35</v>
+        <v>5.99</v>
       </c>
       <c r="M35" t="n">
         <v>0.85</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>5.98</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1870</v>
+        <v>1777</v>
       </c>
       <c r="I36" t="n">
         <v>1835.257354250988</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.36</v>
+        <v>-7.21</v>
       </c>
       <c r="L36" t="n">
-        <v>4.91</v>
+        <v>7.37</v>
       </c>
       <c r="M36" t="n">
         <v>0.03</v>
       </c>
       <c r="N36" t="n">
-        <v>1.31</v>
+        <v>5.57</v>
       </c>
       <c r="O36" t="n">
         <v>2.07</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>10.88</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45518.55208333334</v>
+        <v>45520.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1848.95</v>
+        <v>1886</v>
       </c>
       <c r="I37" t="n">
         <v>1868.434042966153</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.05</v>
+        <v>-6.13</v>
       </c>
       <c r="L37" t="n">
         <v>6.58</v>
       </c>
       <c r="M37" t="n">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="N37" t="n">
         <v>2.44</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>5.11</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1998</v>
+        <v>1990.75</v>
       </c>
       <c r="I38" t="n">
         <v>1997.303230050092</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K38" t="n">
-        <v>5.94</v>
+        <v>5.55</v>
       </c>
       <c r="L38" t="n">
         <v>1.78</v>
       </c>
       <c r="M38" t="n">
-        <v>0.63</v>
+        <v>1.95</v>
       </c>
       <c r="N38" t="n">
         <v>2.03</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.49</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1669.95</v>
+        <v>1703.9</v>
       </c>
       <c r="I39" t="n">
         <v>1686.866080735424</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K39" t="n">
-        <v>16.11</v>
+        <v>14.41</v>
       </c>
       <c r="L39" t="n">
         <v>0.96</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.05</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1721.05</v>
+        <v>1700.4</v>
       </c>
       <c r="I40" t="n">
         <v>1703.100458666452</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K40" t="n">
-        <v>1.01</v>
+        <v>-0.21</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>5.13</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45688.55208333334</v>
+        <v>45689.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1565</v>
+        <v>1631.45</v>
       </c>
       <c r="I41" t="n">
         <v>1599.786092912851</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K41" t="n">
-        <v>7.96</v>
+        <v>4.05</v>
       </c>
       <c r="L41" t="n">
         <v>2.02</v>
@@ -2778,7 +3269,7 @@
         <v>1.74</v>
       </c>
       <c r="N41" t="n">
-        <v>2.76</v>
+        <v>5.56</v>
       </c>
       <c r="O41" t="n">
         <v>-1.35</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1596.1</v>
+        <v>1543.2</v>
       </c>
       <c r="I42" t="n">
         <v>1549.686699530254</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K42" t="n">
-        <v>-2.17</v>
+        <v>-5.41</v>
       </c>
       <c r="L42" t="n">
         <v>5.55</v>
@@ -2835,7 +3338,7 @@
         <v>0.42</v>
       </c>
       <c r="N42" t="n">
-        <v>2.44</v>
+        <v>3.37</v>
       </c>
       <c r="O42" t="n">
         <v>5.56</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>8.17</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45734.38541666666</v>
+        <v>45734.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>1511.15</v>
+        <v>1518.95</v>
       </c>
       <c r="I43" t="n">
         <v>1518.300171740631</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K43" t="n">
-        <v>2.08</v>
+        <v>1.57</v>
       </c>
       <c r="L43" t="n">
         <v>3.67</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>5.64</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45741.38541666666</v>
+        <v>45741.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1475</v>
+        <v>1472.2</v>
       </c>
       <c r="I44" t="n">
         <v>1474.952924986781</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.89</v>
+        <v>-3.08</v>
       </c>
       <c r="L44" t="n">
         <v>3.2</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>5.36</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1465.6</v>
+        <v>1526.25</v>
       </c>
       <c r="I45" t="n">
         <v>1512.775789334751</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>15</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>0.45</v>
+        <v>-3.67</v>
       </c>
       <c r="L45" t="n">
         <v>4.85</v>
@@ -3006,7 +3545,7 @@
         <v>0.04</v>
       </c>
       <c r="N45" t="n">
-        <v>2</v>
+        <v>4.43</v>
       </c>
       <c r="O45" t="n">
         <v>-0.86</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>8.48</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45777.55208333334</v>
+        <v>45779.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1601</v>
+        <v>1565.2</v>
       </c>
       <c r="I46" t="n">
         <v>1578.410659327814</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>4.9</v>
+        <v>2.55</v>
       </c>
       <c r="L46" t="n">
         <v>4.47</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>5.92</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45814.55208333334</v>
+        <v>45817.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1525</v>
+        <v>1543.3</v>
       </c>
       <c r="I47" t="n">
         <v>1532.883454626518</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K47" t="n">
-        <v>2.57</v>
+        <v>1.4</v>
       </c>
       <c r="L47" t="n">
         <v>3.74</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>3.61</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1535</v>
+        <v>1522.3</v>
       </c>
       <c r="I48" t="n">
         <v>1525.661806204761</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.54</v>
+        <v>-1.36</v>
       </c>
       <c r="L48" t="n">
         <v>3.76</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>4.86</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45860.38541666666</v>
+        <v>45860.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>1554.1</v>
+        <v>1579</v>
       </c>
       <c r="I49" t="n">
         <v>1568.136656959413</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.09</v>
+        <v>-3.72</v>
       </c>
       <c r="L49" t="n">
         <v>5.04</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.07</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45869.38541666666</v>
+        <v>45869.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>1511.6</v>
+        <v>1498.9</v>
       </c>
       <c r="I50" t="n">
         <v>1500.209793688833</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.27</v>
+        <v>-5.07</v>
       </c>
       <c r="L50" t="n">
         <v>5.55</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>4.53</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1476</v>
+        <v>1551</v>
       </c>
       <c r="I51" t="n">
         <v>1526.115874119832</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>1.53</v>
+        <v>-3.48</v>
       </c>
       <c r="L51" t="n">
-        <v>1.17</v>
+        <v>5.54</v>
       </c>
       <c r="M51" t="n">
-        <v>0.68</v>
+        <v>3.32</v>
       </c>
       <c r="N51" t="n">
-        <v>1.93</v>
+        <v>5.07</v>
       </c>
       <c r="O51" t="n">
         <v>-1.89</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>5.47</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1569.8</v>
+        <v>1551.9</v>
       </c>
       <c r="I52" t="n">
         <v>1564.546850713033</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K52" t="n">
-        <v>1.21</v>
+        <v>0.06</v>
       </c>
       <c r="L52" t="n">
         <v>2.71</v>
@@ -3405,7 +4028,7 @@
         <v>1.32</v>
       </c>
       <c r="N52" t="n">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="O52" t="n">
         <v>5.07</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>3.73</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45959.38541666666</v>
+        <v>45959.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>1504.2</v>
+        <v>1512</v>
       </c>
       <c r="I53" t="n">
         <v>1507.354871739095</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K53" t="n">
-        <v>3.07</v>
+        <v>2.57</v>
       </c>
       <c r="L53" t="n">
         <v>1.27</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>3.65</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45967.38541666666</v>
+        <v>45967.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1458.8</v>
+        <v>1442</v>
       </c>
       <c r="I54" t="n">
         <v>1458.364019084382</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.52</v>
+        <v>-4.63</v>
       </c>
       <c r="L54" t="n">
-        <v>3.97</v>
+        <v>4.81</v>
       </c>
       <c r="M54" t="n">
         <v>0.53</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.15</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1419.5</v>
+        <v>1439.6</v>
       </c>
       <c r="I55" t="n">
         <v>1438.648326133024</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>56</v>
+        <v>56.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>1.56</v>
+        <v>0.17</v>
       </c>
       <c r="L55" t="n">
         <v>2.95</v>
@@ -3576,7 +4235,7 @@
         <v>0.64</v>
       </c>
       <c r="N55" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="O55" t="n">
         <v>-2.76</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>3.5</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1450</v>
+        <v>1428.5</v>
       </c>
       <c r="I56" t="n">
         <v>1442.586878086238</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K56" t="n">
-        <v>0.72</v>
+        <v>-0.77</v>
       </c>
       <c r="L56" t="n">
         <v>1.52</v>
@@ -3633,7 +4304,7 @@
         <v>0.25</v>
       </c>
       <c r="N56" t="n">
-        <v>1.03</v>
+        <v>1.5</v>
       </c>
       <c r="O56" t="n">
         <v>1.51</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.63</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46056.55208333334</v>
+        <v>46057.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1316</v>
+        <v>1344.9</v>
       </c>
       <c r="I57" t="n">
         <v>1335.146751690485</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K57" t="n">
-        <v>7.88</v>
+        <v>5.85</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>7.3</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1392.7</v>
+        <v>1338.3</v>
       </c>
       <c r="I58" t="n">
         <v>1379.194101269798</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K58" t="n">
-        <v>3.55</v>
+        <v>-0.49</v>
       </c>
       <c r="L58" t="n">
         <v>2.82</v>
       </c>
       <c r="M58" t="n">
-        <v>0.61</v>
+        <v>2.35</v>
       </c>
       <c r="N58" t="n">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="O58" t="n">
         <v>2.13</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>6.77</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1233.8</v>
+        <v>1260.6</v>
       </c>
       <c r="I59" t="n">
         <v>1259.303665198936</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K59" t="n">
-        <v>7.81</v>
+        <v>5.81</v>
       </c>
       <c r="L59" t="n">
         <v>4.95</v>
       </c>
       <c r="M59" t="n">
-        <v>2.18</v>
+        <v>3.58</v>
       </c>
       <c r="N59" t="n">
         <v>4.54</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>7.24</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46134.55208333334</v>
+        <v>46135.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1325</v>
+        <v>1263.1</v>
       </c>
       <c r="I60" t="n">
         <v>1272.508090827792</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K60" t="n">
-        <v>5.11</v>
+        <v>0.2</v>
       </c>
       <c r="L60" t="n">
         <v>2.51</v>
       </c>
       <c r="M60" t="n">
-        <v>1.76</v>
+        <v>2.29</v>
       </c>
       <c r="N60" t="n">
-        <v>0.53</v>
+        <v>5.06</v>
       </c>
       <c r="O60" t="n">
         <v>0.91</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.5</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46189.55208333334</v>
+        <v>46190.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1180.5</v>
+        <v>1195.6</v>
       </c>
       <c r="I61" t="n">
         <v>1192.096759664089</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K61" t="n">
-        <v>6.54</v>
+        <v>5.34</v>
       </c>
       <c r="L61" t="n">
         <v>2.91</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>4.99</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46219.38541666666</v>
+        <v>46219.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>1171.8</v>
+        <v>1167.2</v>
       </c>
       <c r="I62" t="n">
         <v>1167.898120082061</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.99</v>
+        <v>-2.38</v>
       </c>
       <c r="L62" t="n">
         <v>4.63</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>5.27</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46226.55208333334</v>
+        <v>46227.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1205.1</v>
+        <v>1235.5</v>
       </c>
       <c r="I63" t="n">
         <v>1228.726601209905</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-3.25</v>
+        <v>-5.85</v>
       </c>
       <c r="L63" t="n">
-        <v>4.85</v>
+        <v>6.19</v>
       </c>
       <c r="M63" t="n">
         <v>0.5</v>
       </c>
       <c r="N63" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="O63" t="n">
         <v>-0.87</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.99</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46255.55208333334</v>
+        <v>46258.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1265.8</v>
+        <v>1256.4</v>
       </c>
       <c r="I64" t="n">
         <v>1260.248793122149</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K64" t="n">
-        <v>2.45</v>
+        <v>1.69</v>
       </c>
       <c r="L64" t="n">
         <v>3.21</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>4.13</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46308.38541666666</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>1049.9</v>
+        <v>1078.3</v>
       </c>
       <c r="I65" t="n">
         <v>1077.34933244845</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K65" t="n">
-        <v>16.44</v>
+        <v>14.18</v>
       </c>
       <c r="L65" t="n">
         <v>3.4</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>6.32</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1099</v>
+        <v>1068.6</v>
       </c>
       <c r="I66" t="n">
         <v>1069.288636535155</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>6</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>1.92</v>
+        <v>-0.9</v>
       </c>
       <c r="L66" t="n">
         <v>2.87</v>
@@ -4203,7 +4994,7 @@
         <v>0.04</v>
       </c>
       <c r="N66" t="n">
-        <v>1.98</v>
+        <v>2.58</v>
       </c>
       <c r="O66" t="n">
         <v>2.02</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4263,6 +5066,14 @@
       <c r="Q67" t="n">
         <v>12</v>
       </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6365,7 +7176,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.9</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="6">
@@ -6375,7 +7186,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="7">
@@ -6385,7 +7196,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69.2</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8">
@@ -6395,7 +7206,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -6405,7 +7216,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36.2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -6415,7 +7226,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53.7</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="11">
@@ -6425,7 +7236,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -6435,7 +7246,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6445,7 +7256,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>67.7</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="14">
@@ -6455,7 +7266,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.05</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="15">
@@ -6465,7 +7276,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.75</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -6475,7 +7286,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.36</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="17">
@@ -6485,7 +7296,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22.04</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="18">
@@ -6495,7 +7306,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.9</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="19">
@@ -6505,7 +7316,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.41</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="20">
@@ -6515,7 +7326,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.28</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="21">
@@ -6525,7 +7336,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6.58</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -6535,7 +7346,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -6555,7 +7366,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.97</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="25">
@@ -6575,7 +7386,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="27">
@@ -6585,7 +7396,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.54</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="28">
@@ -6595,7 +7406,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
